--- a/03_Features/04_Proteins/c_data/01_sweep.xlsx
+++ b/03_Features/04_Proteins/c_data/01_sweep.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+  <si>
+    <t xml:space="preserve">partition</t>
+  </si>
   <si>
     <t xml:space="preserve">label</t>
   </si>
@@ -49,6 +52,9 @@
     <t xml:space="preserve">given</t>
   </si>
   <si>
+    <t xml:space="preserve">Acute_Interaction</t>
+  </si>
+  <si>
     <t xml:space="preserve">Baseline</t>
   </si>
   <si>
@@ -58,9 +64,18 @@
     <t xml:space="preserve">fcsa_I</t>
   </si>
   <si>
+    <t xml:space="preserve">fcsa_mixed</t>
+  </si>
+  <si>
     <t xml:space="preserve">fcsa_II</t>
   </si>
   <si>
+    <t xml:space="preserve">nfibre_mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nfibre_I</t>
+  </si>
+  <si>
     <t xml:space="preserve">mcsa</t>
   </si>
   <si>
@@ -68,6 +83,9 @@
   </si>
   <si>
     <t xml:space="preserve">1rm_ext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volume_load</t>
   </si>
   <si>
     <t xml:space="preserve">n_samples</t>
@@ -508,388 +526,1057 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>10</v>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1878</v>
+      </c>
+      <c r="E2" t="n">
+        <v>106</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.790766933331937</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="n">
         <v>1882</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E3" t="n">
         <v>63</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.996331871821693</v>
       </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1877</v>
-      </c>
-      <c r="D3" t="n">
-        <v>55</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.93828696756471</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>8</v>
       </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>13</v>
+      <c r="A4" t="n">
+        <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1877</v>
+      </c>
+      <c r="E4" t="n">
+        <v>55</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.93828696756471</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E5" t="n">
+        <v>101</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.752719267811812</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.732743379880961</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E6" t="n">
+        <v>101</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.752719267811812</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.697521563380406</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E7" t="n">
+        <v>101</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.752719267811812</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.687277277094045</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="n">
         <v>1882</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E8" t="n">
         <v>67</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.379554998190309</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.732743379880961</v>
       </c>
-      <c r="I4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
+      <c r="J8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D9" t="n">
+        <v>1882</v>
+      </c>
+      <c r="E9" t="n">
+        <v>67</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.379554998190309</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.697521563380406</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1882</v>
+      </c>
+      <c r="E10" t="n">
+        <v>67</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.379554998190309</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.687277277094045</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1880</v>
+      </c>
+      <c r="E11" t="n">
+        <v>51</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.998227574593045</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.732743379880961</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1880</v>
+      </c>
+      <c r="E12" t="n">
+        <v>51</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.998227574593045</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.697521563380406</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1880</v>
+      </c>
+      <c r="E13" t="n">
+        <v>51</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.998227574593045</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.687277277094045</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="n">
-        <v>1880</v>
-      </c>
-      <c r="D5" t="n">
-        <v>51</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.998227574593045</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.732743379880961</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
+      <c r="D14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="E14" t="n">
+        <v>105</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0525181157138353</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.360338549650662</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1886</v>
+      </c>
+      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.919970290659021</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.360338549650662</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1882</v>
-      </c>
-      <c r="D6" t="n">
-        <v>67</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.379554998190309</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.687277277094045</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
+      <c r="D16" t="n">
+        <v>1878</v>
+      </c>
+      <c r="E16" t="n">
+        <v>72</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.991491852512581</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.360338549650662</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1884</v>
+      </c>
+      <c r="E17" t="n">
+        <v>122</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.390470775989167</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.239926661678627</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1887</v>
+      </c>
+      <c r="E18" t="n">
+        <v>65</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.498796804739247</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.239926661678627</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D19" t="n">
+        <v>1884</v>
+      </c>
+      <c r="E19" t="n">
+        <v>61</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.973965084298466</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.239926661678627</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="n">
-        <v>1880</v>
-      </c>
-      <c r="D7" t="n">
-        <v>51</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.998227574593045</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.687277277094045</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="D20" t="n">
+        <v>1879</v>
+      </c>
+      <c r="E20" t="n">
+        <v>88</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.943881845744298</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.246817985740008</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="n">
         <v>1878</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E21" t="n">
         <v>172</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G21" t="n">
         <v>0.0187248906561852</v>
       </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.246817985740008</v>
       </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="J21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1874</v>
+      </c>
+      <c r="E22" t="n">
+        <v>106</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0901103310978813</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.246817985740008</v>
+      </c>
+      <c r="J22" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="n">
-        <v>1874</v>
-      </c>
-      <c r="D9" t="n">
-        <v>106</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0901103310978813</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.246817985740008</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="D23" t="n">
+        <v>1878</v>
+      </c>
+      <c r="E23" t="n">
+        <v>74</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.998001784129917</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0749361124774681</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="n">
         <v>1876</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E24" t="n">
         <v>248</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
         <v>0.117250298670097</v>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.0749361124774681</v>
       </c>
-      <c r="I10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="J24" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1871</v>
+      </c>
+      <c r="E25" t="n">
+        <v>112</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0830228813403689</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0749361124774681</v>
+      </c>
+      <c r="J25" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
         <v>12</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D26" t="n">
+        <v>1878</v>
+      </c>
+      <c r="E26" t="n">
+        <v>68</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.28046986673098</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.0163014284147838</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1876</v>
+      </c>
+      <c r="E27" t="n">
+        <v>178</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0300965796575914</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.0163014284147838</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="n">
         <v>1871</v>
       </c>
-      <c r="D11" t="n">
-        <v>112</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.0830228813403689</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0749361124774681</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1876</v>
-      </c>
-      <c r="D12" t="n">
-        <v>178</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.0300965796575914</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="E28" t="n">
+        <v>139</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.204994198095565</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.0163014284147838</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J28" t="n">
         <v>7</v>
       </c>
-      <c r="J12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
         <v>12</v>
       </c>
-      <c r="C13" t="n">
-        <v>1871</v>
-      </c>
-      <c r="D13" t="n">
-        <v>139</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.204994198095565</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.0163014284147838</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="D29" t="n">
+        <v>1884</v>
+      </c>
+      <c r="E29" t="n">
+        <v>68</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.114471419873093</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.00187992969459705</v>
+      </c>
+      <c r="J29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1869</v>
+      </c>
+      <c r="E30" t="n">
+        <v>87</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.239560512387797</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.00187992969459705</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1868</v>
+      </c>
+      <c r="E31" t="n">
+        <v>69</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.999421658999322</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.00187992969459705</v>
+      </c>
+      <c r="J31" t="n">
+        <v>8</v>
+      </c>
+      <c r="K31" t="n">
         <v>8</v>
       </c>
     </row>
@@ -909,42 +1596,45 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L1" t="s">
-        <v>27</v>
+        <v>32</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
+      <c r="A2" t="n">
+        <v>5</v>
       </c>
       <c r="B2" t="n">
         <v>45</v>
@@ -953,10 +1643,10 @@
         <v>0.171174550114479</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
         <v>-1.75458696290521</v>
@@ -971,18 +1661,21 @@
         <v>0.0187248906561852</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>17</v>
+      <c r="A3" t="n">
+        <v>7</v>
       </c>
       <c r="B3" t="n">
         <v>42</v>
@@ -991,10 +1684,10 @@
         <v>0.186178867296754</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
         <v>0.772364917062049</v>
@@ -1009,18 +1702,21 @@
         <v>0.0300965796575914</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
+      <c r="A4" t="n">
+        <v>5</v>
       </c>
       <c r="B4" t="n">
         <v>45</v>
@@ -1029,10 +1725,10 @@
         <v>0.171174550114479</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
         <v>0.974645180819184</v>
@@ -1047,13 +1743,16 @@
         <v>0.0362852287588062</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="M4" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1069,27 +1768,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
         <v>1900</v>
@@ -1103,10 +1802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>1900</v>
@@ -1115,6 +1814,23 @@
         <v>0.00000000000000488498130835069</v>
       </c>
       <c r="E3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.00000000000000488498130835069</v>
+      </c>
+      <c r="E4" t="b">
         <v>1</v>
       </c>
     </row>
